--- a/app/views/mission/Mission.xlsx
+++ b/app/views/mission/Mission.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MBF_CODE\nq57-catp\app\views\mission\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E32287-4540-458F-8867-A78AECEEEFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B778319C-89A9-4E9F-928C-9CAA656E6181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{0CE349E1-55CE-4B26-9A0A-629BC4EF4661}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
   <si>
     <t>Tên nhiệm vụ</t>
   </si>
@@ -179,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -205,6 +205,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -574,13 +578,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0787AF9B-0BBF-4DFF-99C2-B37A29E6C80C}">
-  <dimension ref="A1:N217"/>
+  <dimension ref="A1:N216"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35.85546875" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="9" max="9" width="74.140625" customWidth="1"/>
     <col min="10" max="10" width="22.42578125" customWidth="1"/>
@@ -619,68 +623,57 @@
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="12" t="s">
         <v>4</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>14</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -1951,12 +1944,6 @@
       <c r="L216" s="3"/>
       <c r="M216" s="3"/>
       <c r="N216" s="3"/>
-    </row>
-    <row r="217" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K217" s="3"/>
-      <c r="L217" s="3"/>
-      <c r="M217" s="3"/>
-      <c r="N217" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
